--- a/survey_templates/022_real_time_feedback_tracker--survey_templates.xlsx
+++ b/survey_templates/022_real_time_feedback_tracker--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>customer_experience</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What can we improve today?</t>
+          <t>Customer Experience</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,58 +566,58 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How can we improve today?</t>
+          <t>What was the purpose of your visit or interaction with our service today?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What do you think about our customer service team?</t>
+          <t>How would you rate the quality of our service today?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What can we improve today</t>
+          <t>Which departments or teams did you interact with today?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,58 +635,58 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rate your experience</t>
+          <t>What is your email address so we can follow up with you?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>When was your visit?</t>
+          <t>Can you share any feedback about your visit or interaction with our service today?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_7</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What can we do today</t>
+          <t>Do you have any suggestions for our service?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,87 +704,87 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_8</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>How did you find our service today</t>
+          <t>How would you rate the service time today?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_9</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What would you like us to know</t>
+          <t>How would you rate the service quality today?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_10</t>
+          <t>question_9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How can we reach out to you</t>
+          <t>When did you visit our service today?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question_11</t>
+          <t>question_10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What do you think we should change today</t>
+          <t>When did you last contact our service?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,18 +796,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question_12</t>
+          <t>question_11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rate your experience</t>
+          <t>Can you suggest any improvements to our service?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,18 +819,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>question_13</t>
+          <t>question_12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>How can we improve today</t>
+          <t>Are there any specific issues you faced during your interaction with our service?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,18 +842,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>question_14</t>
+          <t>question_13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What can we improve today</t>
+          <t>Do you have any other comments or concerns about our service?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,18 +865,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>question_15</t>
+          <t>question_14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What can we improve today</t>
+          <t>Can you suggest any features or services we could offer that would improve your experience?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>question_16</t>
+          <t>question_15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>How can we improve today</t>
+          <t>Are there any other issues or concerns you would like to mention?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,179 +911,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>question_17</t>
+          <t>question_16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>How can we improve today</t>
+          <t>Question 16</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question_18</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>How can we improve today</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question_19</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>How can we improve today</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question_20</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>How can we improve today</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question_21</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>How can we improve today</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question_22</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>How can we improve today</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question_23</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>How can we improve today</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>question_24</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>How can we improve today</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,153 +965,170 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>question_8_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
